--- a/giro_da_praça_ofertas - SEGUNDA.xlsx
+++ b/giro_da_praça_ofertas - SEGUNDA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DCC4439-741A-426D-AA8E-BF9AE7518947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{725DB4D0-F59C-4FBC-B3AE-A8FF9ED73A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="53">
   <si>
     <t>NOME_PROMOÇÃO</t>
   </si>
@@ -40,40 +40,37 @@
     <t>PROMOÇÃO</t>
   </si>
   <si>
-    <t>SEGUNDA E TERCA - PERECIVEIS 05 E 06/10/26 MATRIZ</t>
+    <t>SEGUNDA E TERCA - PERECIVEIS 12 E 13/10/26 MATRIZ</t>
+  </si>
+  <si>
+    <t>#02 MERCEARIA - CONGELADOS - BATATAS</t>
+  </si>
+  <si>
+    <t>BATATAS CONGELADAS SADIA PCT 400G PALITO PRE-FRITA</t>
   </si>
   <si>
     <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
   </si>
   <si>
-    <t>MANTEIGA QUEIJOLEITE 200G PRIMEIRA QUALIDADE</t>
-  </si>
-  <si>
-    <t>MANTEIGA QUEIJOLEITE 500G DE PRIMEIRA QUALIDADE</t>
+    <t>MANTEIGA COMUM GRANSELETTO 200G COM SAL</t>
   </si>
   <si>
     <t>MARGARINA DELICIA 1KG COM CREME DE LEITE</t>
   </si>
   <si>
-    <t>#02 MERCEARIA - LATICÍNIOS - DERIVADOS LACTEOS</t>
-  </si>
-  <si>
-    <t>CREME DE RICOTA TIROLEZ 200G TRADICIONAL</t>
-  </si>
-  <si>
     <t>#02 MERCEARIA - LATICÍNIOS - QUEIJO</t>
   </si>
   <si>
-    <t>CREAM CHEESE PHILADELPHIA 400G ORIGINAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QUEIJO MUSSARELA PIRACANJUBA 150G FATIADO </t>
+    <t xml:space="preserve">QUEIJO MUSSARELA TIROLEZ 150G FATIADO </t>
+  </si>
+  <si>
+    <t>QUEIJO MUSSARELA TIROLEZ 150G LIGHT FATIADO</t>
   </si>
   <si>
     <t>REQUEIJAO CREMOSO TIROLEZ 200G</t>
   </si>
   <si>
-    <t xml:space="preserve">REQUEIJÃO CREMOSO TIROLEZ 200G LIGHT </t>
+    <t>REQUEIJÃO CREMOSO TIROLEZ 180G PRO+</t>
   </si>
   <si>
     <t>#02 MERCEARIA - PÃES E BOLOS</t>
@@ -82,7 +79,7 @@
     <t>PÃO DE ALHO DI NAPOLI 350G QUEIJO E ERVAS</t>
   </si>
   <si>
-    <t>SEGUNDA - COCOROCO 05/10/26 MATRIZ</t>
+    <t>SEGUNDA - COCOROCO 12/10/26 MATRIZ</t>
   </si>
   <si>
     <t>#03 AÇOUGUE - #01 AVES</t>
@@ -94,34 +91,37 @@
     <t>COXA COM SOBRECOXA DE FRANGO KG</t>
   </si>
   <si>
-    <t>COXA DE FRANGO SADIA PCT 1KG</t>
+    <t>COXA COM SOBRECOXA SADIA 1KG A PASSARINHO</t>
   </si>
   <si>
     <t>COXINHA DA ASA DE FRANGO KG</t>
   </si>
   <si>
-    <t>COXINHA DA ASA DE FRANGO SADIA PCT 1KG DRUMETE</t>
-  </si>
-  <si>
     <t>FIGADO DE FRANGO PERDIGAO KG</t>
   </si>
   <si>
-    <t>FILE PEITO DE FRANGO SADIA PCT 1KG</t>
-  </si>
-  <si>
     <t>FILÉ DE PEITO DE FRANGO KG</t>
   </si>
   <si>
     <t xml:space="preserve">FRANGO AMERICANO KG CONGELADO </t>
   </si>
   <si>
+    <t>FRANGO SADIA PCT 1KG CONGELADO A PASSARINHO TEMPERADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GALINHA NOROESTE KG CONGELADA </t>
+  </si>
+  <si>
     <t>MOELA DE FRANGO PERDIGÃO BDJ 1KG</t>
   </si>
   <si>
     <t>PEITO DE FRANGO KG INTEIRO</t>
   </si>
   <si>
-    <t>SEGUNDA - ACOUGUE 05/10/26 MATRIZ</t>
+    <t>PEITO DE FRANGO SADIA 1KG A PASSARINHO</t>
+  </si>
+  <si>
+    <t>SEGUNDA - ACOUGUE 12/10/26 MATRIZ</t>
   </si>
   <si>
     <t>#03 AÇOUGUE - #02 BOVINA</t>
@@ -130,54 +130,42 @@
     <t>ACEM BOVINO COM OSSO KG</t>
   </si>
   <si>
-    <t>ACEM BOVINO KG</t>
-  </si>
-  <si>
-    <t>CARNE DE SOL BOVINA PICADA KG</t>
+    <t>CARNE BOVINA SERENADA KG</t>
+  </si>
+  <si>
+    <t>CARNE DE SOL KG SEGUNDA</t>
   </si>
   <si>
     <t>CARNE MOIDA KG</t>
   </si>
   <si>
-    <t>CHAMBARI KG</t>
+    <t>COSTELA BOVINA KG</t>
   </si>
   <si>
     <t>COXÃO MOLE KG</t>
   </si>
   <si>
-    <t>MUSCULO BOVINO KG</t>
-  </si>
-  <si>
-    <t>#03 AÇOUGUE - #03 SUÍNA</t>
-  </si>
-  <si>
-    <t>PELE SUINA KG</t>
+    <t>FIGADO BOVINO KG</t>
+  </si>
+  <si>
+    <t>LINGUA BOVINA KG</t>
   </si>
   <si>
     <t>#03 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
   </si>
   <si>
-    <t>LINGUIÇA CALABRESA FRESCAL FRIMESA PCT 1KG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LINGUIÇA DEFUMADA SEARA 215G FININHA </t>
-  </si>
-  <si>
     <t>LINGUIÇA GROSSA SUPER FRANGO KG</t>
   </si>
   <si>
+    <t>LINGUIÇA MISTA FININHA DEFUMADA SADIA 215G</t>
+  </si>
+  <si>
+    <t>LINGUIÇA MISTA PERDIGAO 215G FININHA DEFUMADA</t>
+  </si>
+  <si>
     <t>LINGUIÇA SUPER FRANGO 400G DEFUMADA</t>
   </si>
   <si>
-    <t>LINGUIÇA TOSCANA PERDIGÃO NABRASA 600G COM PIMENTA BIQUINHO</t>
-  </si>
-  <si>
-    <t>MORTADELA MISTA PERDIGÃO KG</t>
-  </si>
-  <si>
-    <t>MORTADELA SUÍNA SADIA 1KG</t>
-  </si>
-  <si>
     <t xml:space="preserve">SALAME PERDIGÃO 100GR FATIADO </t>
   </si>
   <si>
@@ -187,10 +175,10 @@
     <t>#03 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
   </si>
   <si>
-    <t>TEKITOS SEARA 300G</t>
-  </si>
-  <si>
-    <t>FRANGO, QUEIJO COM OREGANO</t>
+    <t>STEAK EMPANADO SADIA 100G FRANGO</t>
+  </si>
+  <si>
+    <t>TEKITOS SEARA 300G QUEIJO COM OREGANO</t>
   </si>
 </sst>
 </file>
@@ -200,7 +188,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -220,31 +208,21 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <sz val="16"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="16"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -288,7 +266,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -296,32 +274,22 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -627,15 +595,15 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
-  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:F38"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.5703125" style="11" customWidth="1"/>
-    <col min="5" max="5" width="23.85546875" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -645,394 +613,394 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="42" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="5">
-        <v>336816</v>
-      </c>
-      <c r="D2" s="12" t="s">
+      <c r="C2" s="3">
+        <v>227503</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="10"/>
-      <c r="F2" s="6">
+      <c r="E2" s="5"/>
+      <c r="F2" s="7">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3">
+        <v>289484</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="7">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="3">
+        <v>276943</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="7">
+        <v>15.59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="3">
+        <v>178976</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="7">
+        <v>10.59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="3">
+        <v>230383</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="7">
         <v>10.99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="5">
-        <v>336817</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="10"/>
-      <c r="F3" s="6">
-        <v>23.99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="42" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="5">
-        <v>276943</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="10"/>
-      <c r="F4" s="6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="3">
+        <v>104770</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="7">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3">
+        <v>348374</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="7">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="3">
+        <v>220822</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="7">
         <v>14.99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="42" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="5">
-        <v>258461</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="6">
-        <v>9.69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="5">
-        <v>162504</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="6">
-        <v>37.99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="5">
-        <v>158733</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="6">
-        <v>12.49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="42" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="5">
-        <v>104770</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="6">
-        <v>9.69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="42" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="5">
-        <v>133484</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="10"/>
-      <c r="F9" s="6">
-        <v>9.69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="42" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="5">
-        <v>220822</v>
-      </c>
-      <c r="D10" s="12" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="6">
-        <v>14.99</v>
+      <c r="B11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="3">
+        <v>105842</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="7">
+        <v>13.89</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="5">
-        <v>105842</v>
-      </c>
-      <c r="D12" s="12" t="s">
+      <c r="C12" s="3">
+        <v>105838</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="10"/>
-      <c r="F12" s="6">
-        <v>13.89</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="42" x14ac:dyDescent="0.25">
+      <c r="E12" s="5"/>
+      <c r="F12" s="7">
+        <v>9.39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="5">
-        <v>105838</v>
-      </c>
-      <c r="D13" s="12" t="s">
+      <c r="C13" s="3">
+        <v>111324</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="10"/>
-      <c r="F13" s="6">
-        <v>9.39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="42" x14ac:dyDescent="0.25">
+      <c r="E13" s="5"/>
+      <c r="F13" s="7">
+        <v>20.69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="5">
-        <v>104602</v>
-      </c>
-      <c r="D14" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="3">
+        <v>105840</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="6">
+      <c r="E14" s="5"/>
+      <c r="F14" s="7">
+        <v>11.59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="3">
+        <v>306504</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="7">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="3">
+        <v>109597</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="7">
+        <v>17.89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="3">
+        <v>119927</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="5"/>
+      <c r="F17" s="7">
+        <v>10.89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="3">
+        <v>108788</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="5"/>
+      <c r="F18" s="7">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="3">
+        <v>185934</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="5"/>
+      <c r="F19" s="7">
+        <v>10.89</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="3">
+        <v>195365</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="5"/>
+      <c r="F20" s="7">
         <v>13.99</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="42" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="5">
-        <v>105840</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="10"/>
-      <c r="F15" s="6">
-        <v>11.59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="5">
-        <v>108785</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="10"/>
-      <c r="F16" s="6">
-        <v>17.989999999999998</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="42" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="5">
-        <v>306504</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="10"/>
-      <c r="F17" s="6">
-        <v>6.99</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="42" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="5">
-        <v>108856</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="10"/>
-      <c r="F18" s="6">
-        <v>23.99</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="42" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="C21" s="3">
+        <v>150768</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="5"/>
+      <c r="F21" s="7">
+        <v>13.49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="5">
-        <v>109597</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" s="10"/>
-      <c r="F19" s="6">
-        <v>17.89</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="42" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="5">
-        <v>119927</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E20" s="10"/>
-      <c r="F20" s="6">
-        <v>10.89</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="42" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="5">
-        <v>195365</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="10"/>
-      <c r="F21" s="6">
-        <v>13.59</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="42" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" s="5">
-        <v>150768</v>
-      </c>
-      <c r="D22" s="12" t="s">
+      <c r="C22" s="3">
+        <v>302029</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E22" s="10"/>
-      <c r="F22" s="6">
-        <v>13.49</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="42" x14ac:dyDescent="0.25">
+      <c r="E22" s="5"/>
+      <c r="F22" s="7">
+        <v>22.99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="3">
         <v>157014</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E23" s="10"/>
-      <c r="F23" s="6">
+      <c r="E23" s="5"/>
+      <c r="F23" s="7">
         <v>15.99</v>
       </c>
     </row>
@@ -1043,33 +1011,33 @@
       <c r="B24" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="5">
-        <v>105470</v>
-      </c>
-      <c r="D24" s="12" t="s">
+      <c r="C24" s="3">
+        <v>105457</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E24" s="10"/>
-      <c r="F24" s="6">
-        <v>27.99</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="42" x14ac:dyDescent="0.25">
+      <c r="E24" s="5"/>
+      <c r="F24" s="7">
+        <v>37.99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="5">
-        <v>110573</v>
-      </c>
-      <c r="D25" s="12" t="s">
+      <c r="C25" s="3">
+        <v>105456</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E25" s="10"/>
-      <c r="F25" s="6">
-        <v>31.99</v>
+      <c r="E25" s="5"/>
+      <c r="F25" s="7">
+        <v>37.99</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1079,14 +1047,14 @@
       <c r="B26" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="3">
         <v>105468</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E26" s="10"/>
-      <c r="F26" s="6">
+      <c r="E26" s="5"/>
+      <c r="F26" s="7">
         <v>20.99</v>
       </c>
     </row>
@@ -1097,15 +1065,15 @@
       <c r="B27" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="5">
-        <v>105458</v>
-      </c>
-      <c r="D27" s="12" t="s">
+      <c r="C27" s="3">
+        <v>105471</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E27" s="10"/>
-      <c r="F27" s="6">
-        <v>20.99</v>
+      <c r="E27" s="5"/>
+      <c r="F27" s="7">
+        <v>24.99</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1115,15 +1083,15 @@
       <c r="B28" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28" s="3">
         <v>105435</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E28" s="10"/>
-      <c r="F28" s="6">
-        <v>42.99</v>
+      <c r="E28" s="5"/>
+      <c r="F28" s="7">
+        <v>43.99</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1133,15 +1101,15 @@
       <c r="B29" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="5">
-        <v>105475</v>
-      </c>
-      <c r="D29" s="12" t="s">
+      <c r="C29" s="3">
+        <v>106065</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E29" s="10"/>
-      <c r="F29" s="6">
-        <v>23.99</v>
+      <c r="E29" s="5"/>
+      <c r="F29" s="7">
+        <v>10.99</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1149,204 +1117,166 @@
         <v>33</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="3">
+        <v>105467</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C30" s="5">
-        <v>106052</v>
-      </c>
-      <c r="D30" s="12" t="s">
+      <c r="E30" s="5"/>
+      <c r="F30" s="7">
+        <v>27.89</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E30" s="10"/>
-      <c r="F30" s="6">
-        <v>16.989999999999998</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="42" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="2" t="s">
+      <c r="C31" s="3">
+        <v>228422</v>
+      </c>
+      <c r="D31" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C31" s="5">
-        <v>209710</v>
-      </c>
-      <c r="D31" s="12" t="s">
+      <c r="E31" s="5"/>
+      <c r="F31" s="7">
+        <v>19.489999999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" s="3">
+        <v>289127</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E31" s="10"/>
-      <c r="F31" s="6">
-        <v>32.99</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="42" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C32" s="5">
-        <v>227259</v>
-      </c>
-      <c r="D32" s="12" t="s">
+      <c r="E32" s="5"/>
+      <c r="F32" s="7">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="3">
+        <v>289126</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E32" s="10"/>
-      <c r="F32" s="6">
-        <v>6.99</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="42" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C33" s="5">
-        <v>228422</v>
-      </c>
-      <c r="D33" s="12" t="s">
+      <c r="E33" s="5"/>
+      <c r="F33" s="7">
+        <v>8.2899999999999991</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="3">
+        <v>292399</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E33" s="10"/>
-      <c r="F33" s="6">
-        <v>19.489999999999998</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="42" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C34" s="5">
-        <v>292399</v>
-      </c>
-      <c r="D34" s="12" t="s">
+      <c r="E34" s="5"/>
+      <c r="F34" s="7">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="3">
+        <v>184045</v>
+      </c>
+      <c r="D35" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E34" s="10"/>
-      <c r="F34" s="6">
-        <v>9.99</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="63" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C35" s="5">
-        <v>183189</v>
-      </c>
-      <c r="D35" s="12" t="s">
+      <c r="E35" s="5"/>
+      <c r="F35" s="7">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C36" s="3">
+        <v>227341</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E35" s="10"/>
-      <c r="F35" s="6">
-        <v>29.99</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="42" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C36" s="5">
-        <v>105765</v>
-      </c>
-      <c r="D36" s="12" t="s">
+      <c r="E36" s="5"/>
+      <c r="F36" s="7">
+        <v>7.89</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E36" s="10"/>
-      <c r="F36" s="6">
-        <v>11.99</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="42" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C37" s="5">
-        <v>108558</v>
-      </c>
-      <c r="D37" s="12" t="s">
+      <c r="C37" s="3">
+        <v>170464</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E37" s="10"/>
-      <c r="F37" s="6">
-        <v>11.99</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="42" x14ac:dyDescent="0.25">
+      <c r="E37" s="5"/>
+      <c r="F37" s="7">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C38" s="5">
-        <v>184045</v>
-      </c>
-      <c r="D38" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" s="3">
+        <v>127328</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E38" s="10"/>
-      <c r="F38" s="6">
-        <v>10.99</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="42" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C39" s="5">
-        <v>227341</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E39" s="10"/>
-      <c r="F39" s="6">
-        <v>7.89</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="42" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C40" s="5">
-        <v>138538</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E40" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="F40" s="6">
+      <c r="E38" s="5"/>
+      <c r="F38" s="7">
         <v>8.69</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="89" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;LGIRO DA PRAÇA - SEGUNDA&amp;C&amp;P - &amp;N</oddHeader>
   </headerFooter>
